--- a/Excel/MonsterQualityConfig.xlsx
+++ b/Excel/MonsterQualityConfig.xlsx
@@ -1204,7 +1204,7 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
@@ -1233,7 +1233,7 @@
         <v>1.5</v>
       </c>
       <c r="G8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1">
         <v>3</v>
@@ -1262,7 +1262,7 @@
         <v>1.8</v>
       </c>
       <c r="G9" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H9" s="1">
         <v>5</v>
